--- a/artfynd/S 312-2024 artfynd.xlsx
+++ b/artfynd/S 312-2024 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>134588555</v>
       </c>
       <c r="B15" t="n">
-        <v>57967</v>
+        <v>58000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 312-2024 artfynd.xlsx
+++ b/artfynd/S 312-2024 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>134588555</v>
       </c>
       <c r="B15" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 312-2024 artfynd.xlsx
+++ b/artfynd/S 312-2024 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>134588555</v>
       </c>
       <c r="B15" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 312-2024 artfynd.xlsx
+++ b/artfynd/S 312-2024 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>134588555</v>
       </c>
       <c r="B15" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 312-2024 artfynd.xlsx
+++ b/artfynd/S 312-2024 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>134588555</v>
       </c>
       <c r="B15" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 312-2024 artfynd.xlsx
+++ b/artfynd/S 312-2024 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>134588555</v>
       </c>
       <c r="B15" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 312-2024 artfynd.xlsx
+++ b/artfynd/S 312-2024 artfynd.xlsx
@@ -2218,7 +2218,7 @@
         <v>134588555</v>
       </c>
       <c r="B15" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
